--- a/report_unmatched_shortage.xlsx
+++ b/report_unmatched_shortage.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +26,38 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +65,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,86 +467,90 @@
   </sheetPr>
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Chỉ Tiêu</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chỉ Tiêu Thống Kê</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Giá Trị</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Tổng số dòng âm tại Kho 50 &amp; 62</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>2,814 dòng</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Tổng số lượng âm cần xử lý</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>382,450</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Số lượt nhập tự động (Lô nguyên vẹn)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>71 lượt</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Số lượng âm đã giải quyết ngay</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>109,173</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Số lượng còn thiếu (Chờ tách lẻ / nhập thêm)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>273,277</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Tỷ lệ cấn trừ ngay không cần tách lẻ</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>28.55%</t>
         </is>
@@ -514,3461 +569,3470 @@
   </sheetPr>
   <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="82" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Stock Code</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Mã Vật Tư (Stock Code)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Kho Bị Âm</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Tổng Số Lượng Âm</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Đã Bù Trọn Vẹn</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Còn Thiếu (Chờ Tách Lẻ/Nhập Thêm)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Còn Thiếu (Chờ Tách Lẻ)</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Tỷ Lệ Bù (%)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Lý Do</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>3400250001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>3405010201</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>275</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="4" t="n">
         <v>429</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="5" t="n">
         <v>39.1</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>3405020201</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>3405030101</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="4" t="n">
         <v>361</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="4" t="n">
         <v>343</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="5" t="n">
         <v>51.3</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>3405040101</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>330</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="4" t="n">
         <v>377</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>3405050001</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>2822</v>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>2822</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>3405070101</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>3405090201</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>3405100201</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>560</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="4" t="n">
         <v>147</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="5" t="n">
         <v>79.2</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>3405110101</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="4" t="n">
         <v>204</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>3405120101</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>280</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="4" t="n">
         <v>427</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="5" t="n">
         <v>39.6</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>3405130101</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="4" t="n">
         <v>654</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="5" t="n">
         <v>7.1</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>3405140101</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>3405170101</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>3405190101</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>3405210301</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>1240</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="4" t="n">
         <v>171</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="5" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>3405230101</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="4" t="n">
         <v>615</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="4" t="n">
         <v>796</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="5" t="n">
         <v>43.6</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>3405250101</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>3405350001</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>497</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="4" t="n">
         <v>207</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="5" t="n">
         <v>70.59999999999999</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>3405360001</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>195</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="4" t="n">
         <v>512</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="5" t="n">
         <v>27.6</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>3405710001</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>3407810101</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="4" t="n">
         <v>670</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="5" t="n">
         <v>95.2</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>3407820101</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="4" t="n">
         <v>250</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="4" t="n">
         <v>457</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="5" t="n">
         <v>35.4</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>3407830101</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="4" t="n">
         <v>204</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>3407840101</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="4" t="n">
         <v>207</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="5" t="n">
         <v>70.7</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>3407870001</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="D27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>3407880001</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="4" t="n">
         <v>507</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="5" t="n">
         <v>28.3</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>3419840001</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
         <v>289</v>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>289</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>3423010001</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="D30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>3423020001</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="4" t="n">
         <v>673</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>3423030001</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="D32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>3423040001</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="D33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>3423130001</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
         <v>704</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="4" t="n">
         <v>304</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="5" t="n">
         <v>56.8</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>3423140001</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
         <v>707</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>230</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="4" t="n">
         <v>477</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="5" t="n">
         <v>32.5</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>3434210001</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
         <v>671</v>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="D36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>671</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>3434220001</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
         <v>819</v>
       </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="D37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>819</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>3437070201</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
         <v>942</v>
       </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>942</v>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>3437150201</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>3440050101</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
         <v>161</v>
       </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
         <v>161</v>
       </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>3443650201</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>3447230001</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
         <v>2007</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>1310</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="4" t="n">
         <v>697</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="5" t="n">
         <v>65.3</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>3447270001</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
         <v>1849</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>1803</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="5" t="n">
         <v>97.5</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>3447510001</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
         <v>1997</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="4" t="n">
         <v>1951</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>3447520001</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
         <v>1859</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>964</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="4" t="n">
         <v>895</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="5" t="n">
         <v>51.9</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>3447530001</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
         <v>2007</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>1470</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="4" t="n">
         <v>537</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="5" t="n">
         <v>73.2</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>3447970001</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
         <v>1956</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>890</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="4" t="n">
         <v>1066</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="5" t="n">
         <v>45.5</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>3447990001</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
         <v>1084</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="4" t="n">
         <v>850</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="4" t="n">
         <v>234</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="5" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>3448000001</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
         <v>1614</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>1080</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="4" t="n">
         <v>534</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="5" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>3451270001</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
         <v>943</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="4" t="n">
         <v>443</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>3451280001</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
         <v>846</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="4" t="n">
         <v>556</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="5" t="n">
         <v>34.3</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>3453530001</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
         <v>1849</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="4" t="n">
         <v>1455</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="4" t="n">
         <v>394</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="5" t="n">
         <v>78.7</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>3457800001</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="D53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="F53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>3462260001</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
+      <c r="D54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="F54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>3464140001</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
         <v>1898</v>
       </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
+      <c r="D55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="4" t="n">
         <v>1898</v>
       </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="F55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>3464230001</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
         <v>211</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="4" t="n">
         <v>191</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="5" t="n">
         <v>9.5</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>3464670001</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
         <v>1948</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="4" t="n">
         <v>1050</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="4" t="n">
         <v>898</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>3464730001</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
         <v>978</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="4" t="n">
         <v>878</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="5" t="n">
         <v>10.2</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>3465830001</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
         <v>1855</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>650</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="4" t="n">
         <v>1205</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>3465950101</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
         <v>211</v>
       </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
+      <c r="D60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>211</v>
       </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>3465960101</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
         <v>808</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>411</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="4" t="n">
         <v>397</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="5" t="n">
         <v>50.9</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>3465990001</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
         <v>489</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="5" t="n">
         <v>81.8</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>3466000001</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="n">
+      <c r="D63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="F63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>3888130001</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
         <v>346</v>
       </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
+      <c r="D64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="4" t="n">
         <v>346</v>
       </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>5100300051</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
         <v>5905</v>
       </c>
-      <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="n">
+      <c r="D65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>5905</v>
       </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>5100330051</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="n">
+      <c r="D66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>5100330051</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
         <v>1442</v>
       </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="D67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="4" t="n">
         <v>1442</v>
       </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="F67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>5100430051PD</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
         <v>1978</v>
       </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
+      <c r="D68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>1978</v>
       </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>5100630051</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
         <v>1978</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="4" t="n">
         <v>669</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="4" t="n">
         <v>1309</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="5" t="n">
         <v>33.8</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>7100030051PA</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
         <v>4252</v>
       </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
+      <c r="D70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="4" t="n">
         <v>4252</v>
       </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>7100030051PA</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
         <v>34340</v>
       </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
+      <c r="D71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="4" t="n">
         <v>34340</v>
       </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="F71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>7100040051PA</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
         <v>7437</v>
       </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
+      <c r="D72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="4" t="n">
         <v>7437</v>
       </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>7100060051</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
         <v>4025</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>1489</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="4" t="n">
         <v>2536</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>7100060051PA</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
         <v>1332</v>
       </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
+      <c r="D74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="4" t="n">
         <v>1332</v>
       </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>7100060051PA</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
         <v>56741</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>24500</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="4" t="n">
         <v>32241</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>7100070051</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
         <v>1395</v>
       </c>
-      <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="D76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="4" t="n">
         <v>1395</v>
       </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>7100070051PA</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="n">
+      <c r="D77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>7100090051PA</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="n">
+      <c r="D78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>7100090051PA</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
         <v>2897</v>
       </c>
-      <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="n">
+      <c r="D79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="4" t="n">
         <v>2897</v>
       </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>7100150051PA</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
         <v>11313</v>
       </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="n">
+      <c r="D80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="4" t="n">
         <v>11313</v>
       </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>7100180021</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n">
         <v>1929</v>
       </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="n">
+      <c r="D81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4" t="n">
         <v>1929</v>
       </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>7100180051</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n">
         <v>4051</v>
       </c>
-      <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="n">
+      <c r="D82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="4" t="n">
         <v>4051</v>
       </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>7100180051</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n">
         <v>2010</v>
       </c>
-      <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="n">
+      <c r="D83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="4" t="n">
         <v>2010</v>
       </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="F83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>7100240051</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
         <v>1978</v>
       </c>
-      <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="n">
+      <c r="D84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="4" t="n">
         <v>1978</v>
       </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>7101130051</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
         <v>5757</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="4" t="n">
         <v>3757</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85" s="5" t="n">
         <v>34.7</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>7103970051</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n">
         <v>2127</v>
       </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="n">
+      <c r="D86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="4" t="n">
         <v>2127</v>
       </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>7109830051PD</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
         <v>9631</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="4" t="n">
         <v>7631</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>7130110001</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n">
         <v>3896</v>
       </c>
-      <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="n">
+      <c r="D88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="4" t="n">
         <v>3896</v>
       </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>7130310001</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n">
         <v>8542</v>
       </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="n">
+      <c r="D89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="4" t="n">
         <v>8542</v>
       </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>7150020001</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n">
         <v>1956</v>
       </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
+      <c r="D90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="4" t="n">
         <v>1956</v>
       </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>7150090001</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n">
         <v>4233</v>
       </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="n">
+      <c r="D91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="4" t="n">
         <v>4233</v>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>7150110001</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
         <v>1739</v>
       </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="n">
+      <c r="D92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="4" t="n">
         <v>1739</v>
       </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>7150110001</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n">
         <v>9810</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="4" t="n">
         <v>7000</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="4" t="n">
         <v>2810</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93" s="5" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>7150150001</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n">
         <v>3596</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="4" t="n">
         <v>1900</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="4" t="n">
         <v>1696</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94" s="5" t="n">
         <v>52.8</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>7150160001</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
         <v>1396</v>
       </c>
-      <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="n">
+      <c r="D95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="4" t="n">
         <v>1396</v>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>7150170001</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n">
         <v>8318</v>
       </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="n">
+      <c r="D96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="4" t="n">
         <v>8318</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>7150180001</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="n">
         <v>6258</v>
       </c>
-      <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="n">
+      <c r="D97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="4" t="n">
         <v>6258</v>
       </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>7150180001</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n">
         <v>12551</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="4" t="n">
         <v>7700</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98" s="4" t="n">
         <v>4851</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98" s="5" t="n">
         <v>61.3</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>7150190001</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n">
         <v>2448</v>
       </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
+      <c r="D99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="4" t="n">
         <v>2448</v>
       </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="inlineStr">
+      <c r="F99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>7150200001</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
         <v>8527</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="4" t="n">
         <v>8000</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100" s="4" t="n">
         <v>527</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100" s="5" t="n">
         <v>93.8</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>7150780201</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" s="4" t="n">
         <v>1211</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>7150790001</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n">
         <v>1429</v>
       </c>
-      <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="n">
+      <c r="D102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="4" t="n">
         <v>1429</v>
       </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="F102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>7151480001</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="n">
         <v>1930</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103" s="4" t="n">
         <v>1180</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103" s="5" t="n">
         <v>38.9</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>7151490001</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="n">
         <v>1429</v>
       </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="n">
+      <c r="D104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="4" t="n">
         <v>1429</v>
       </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="inlineStr">
+      <c r="F104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>7151940001</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="n">
         <v>2858</v>
       </c>
-      <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="n">
+      <c r="D105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="4" t="n">
         <v>2858</v>
       </c>
-      <c r="F105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" t="inlineStr">
+      <c r="F105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>7151940001</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="n">
         <v>2898</v>
       </c>
-      <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="n">
+      <c r="D106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="4" t="n">
         <v>2898</v>
       </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="inlineStr">
+      <c r="F106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>7151970001</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="n">
         <v>9832</v>
       </c>
-      <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="n">
+      <c r="D107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="4" t="n">
         <v>9832</v>
       </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="inlineStr">
+      <c r="F107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>7151980001</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n">
         <v>3926</v>
       </c>
-      <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="n">
+      <c r="D108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="4" t="n">
         <v>3926</v>
       </c>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>7152000001</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
         <v>1365</v>
       </c>
-      <c r="D109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" t="n">
+      <c r="D109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="4" t="n">
         <v>1365</v>
       </c>
-      <c r="F109" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" t="inlineStr">
+      <c r="F109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>7156770001</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="n">
         <v>34383</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="4" t="n">
         <v>30500</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110" s="4" t="n">
         <v>3883</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110" s="5" t="n">
         <v>88.7</v>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>7157090001</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="n">
         <v>1429</v>
       </c>
-      <c r="D111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" t="n">
+      <c r="D111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="4" t="n">
         <v>1429</v>
       </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="inlineStr">
+      <c r="F111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>7157360001</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="n">
         <v>4004</v>
       </c>
-      <c r="D112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" t="n">
+      <c r="D112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="4" t="n">
         <v>4004</v>
       </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="inlineStr">
+      <c r="F112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>7157380001</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="n">
         <v>1685</v>
       </c>
-      <c r="D113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" t="n">
+      <c r="D113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="4" t="n">
         <v>1685</v>
       </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="inlineStr">
+      <c r="F113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>7157420001</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="n">
         <v>3629</v>
       </c>
-      <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="n">
+      <c r="D114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="4" t="n">
         <v>3629</v>
       </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="inlineStr">
+      <c r="F114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>7159480001</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n">
         <v>1867</v>
       </c>
-      <c r="D115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" t="n">
+      <c r="D115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="4" t="n">
         <v>1867</v>
       </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="inlineStr">
+      <c r="F115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>7159840001</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n">
         <v>1956</v>
       </c>
-      <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="n">
+      <c r="D116" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="4" t="n">
         <v>1956</v>
       </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="inlineStr">
+      <c r="F116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>7200260001</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n">
         <v>1411</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" s="4" t="n">
         <v>911</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117" s="5" t="n">
         <v>35.4</v>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>7200260001</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
         <v>1955</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="4" t="n">
         <v>989</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118" s="4" t="n">
         <v>966</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118" s="5" t="n">
         <v>50.6</v>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>991140007300</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n">
         <v>1858</v>
       </c>
-      <c r="D119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" t="n">
+      <c r="D119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="4" t="n">
         <v>1858</v>
       </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" t="inlineStr">
+      <c r="F119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>Các lô dương còn lại có số lượng lớn hơn phần thiếu (Cần tách lẻ) hoặc hết tồn</t>
         </is>
